--- a/astro-site/public/dl/plan-negocio-taqueria/calculadora-trompo-escandallo-taqueria.xlsx
+++ b/astro-site/public/dl/plan-negocio-taqueria/calculadora-trompo-escandallo-taqueria.xlsx
@@ -3772,7 +3772,7 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. Seguridad alimentaria. El cono montado y adobado es un preparado de carne: manténlo a 4 °C como máximo hasta que entre al asador, mide con sonda y registra la temperatura en tu plan de APPCC. Pregunta a tu ayuntamiento y a tu comunidad por lo que exigen en tu zona.</t>
+          <t>5. Seguridad alimentaria. El cono montado y adobado es un preparado de carne: mantenlo a 4 °C como máximo hasta que entre al asador, mide con sonda y registra la temperatura en tu plan de APPCC. Pregunta a tu ayuntamiento y a tu comunidad por lo que exigen en tu zona.</t>
         </is>
       </c>
     </row>
